--- a/evaluation_forms/016_film_course_participant_evaluation--evaluation_forms.xlsx
+++ b/evaluation_forms/016_film_course_participant_evaluation--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'highly_satisfied',_'value':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Satisfied', 'value': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied',_'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied', 'value': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_5}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_2}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 2}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_1}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': 1}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'much_improved',_'value':_5}</t>
+          <t>much_improved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Much Improved', 'value': 5}</t>
+          <t>Much Improved</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_improved',_'value':_4}</t>
+          <t>moderately_improved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately Improved', 'value': 4}</t>
+          <t>Moderately Improved</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_improved',_'value':_3}</t>
+          <t>slightly_improved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly Improved', 'value': 3}</t>
+          <t>Slightly Improved</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_improved',_'value':_2}</t>
+          <t>not_improved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not Improved', 'value': 2}</t>
+          <t>Not Improved</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'much_worse',_'value':_1}</t>
+          <t>much_worse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Much Worse', 'value': 1}</t>
+          <t>Much Worse</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_2}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 2}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_1}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All', 'value': 1}</t>
+          <t>Not at All</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_5}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_2}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 2}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_1}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All', 'value': 1}</t>
+          <t>Not at All</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_5}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_2}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor', 'value': 2}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_1}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All', 'value': 1}</t>
+          <t>Not at All</t>
         </is>
       </c>
     </row>
